--- a/downloads/exercises/intermedio-m04-m04-l04-practice-01.xlsx
+++ b/downloads/exercises/intermedio-m04-m04-l04-practice-01.xlsx
@@ -512,6 +512,96 @@
         <x:v>Vie-sáb</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="4" t="inlineStr">
+        <x:is>
+          <x:t>Plazos con DIA.LAB.INTL: fecha, no conteo</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="9" t="inlineStr">
+        <x:is>
+          <x:t>Fecha inicial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="9" t="inlineStr">
+        <x:is>
+          <x:t>Plazo laborable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="9" t="inlineStr">
+        <x:is>
+          <x:t>Código</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="9" t="inlineStr">
+        <x:is>
+          <x:t>DIA.LAB.INTL / WORKDAY.INTL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="9" t="inlineStr">
+        <x:is>
+          <x:t>Comprobación por calendario</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F14" s="9" t="inlineStr">
+        <x:is>
+          <x:t>Caso</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G14" s="9" t="inlineStr">
+        <x:is>
+          <x:t>Interpretación</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="14" t="n">
+        <x:v>46278</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D15" s="16"/>
+      <x:c r="E15" s="16"/>
+      <x:c r="F15" s="0" t="inlineStr">
+        <x:is>
+          <x:t>Avance +5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G15" s="4" t="inlineStr">
+        <x:is>
+          <x:t>Plazo positivo: fecha futura; el inicio no consume el plazo.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="14" t="n">
+        <x:v>46284</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="n">
+        <x:v>-5</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D16" s="16"/>
+      <x:c r="E16" s="16"/>
+      <x:c r="F16" s="0" t="inlineStr">
+        <x:is>
+          <x:t>Retroceso -5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G16" s="4" t="inlineStr">
+        <x:is>
+          <x:t>Plazo negativo: fecha anterior; el inicio no consume el plazo.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
@@ -558,6 +648,27 @@
         <x:v>5. No elijas un código de fin de semana sin documentar qué calendario laboral representa.</x:v>
       </x:c>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="4" t="inlineStr">
+        <x:is>
+          <x:t>6. Completa D15:D16 con DIA.LAB.INTL para los plazos +5 y -5, conservando código 7 y $J$5:$J$8.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="4" t="inlineStr">
+        <x:is>
+          <x:t>7. Usa =DIA.LAB.INTL(A15;B15;C15;$J$5:$J$8) y copia a la fila 16; en inglés y con coma: =WORKDAY.INTL(A15,B15,C15,$J$5:$J$8). Aplica formato de fecha a D15:D16.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="4" t="inlineStr">
+        <x:is>
+          <x:t>8. Antes de calcular, predice. En E15:E16 enumera cinco días admitidos en la dirección del plazo, sin contar el inicio ni viernes, sábado o festivos. Distingue fecha de plazo de conteo inclusivo de DIAS.LAB.INTL.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -603,6 +714,42 @@
         <x:v>27/08/2026 — La explicación de la plataforma es autocontenida; esta URL respalda sintaxis y comportamiento técnico.</x:v>
       </x:c>
     </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="0" t="inlineStr">
+        <x:is>
+          <x:t>Fuente — plazo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="4" t="inlineStr">
+        <x:is>
+          <x:t>Microsoft Support — Función DIA.LAB.INTL</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="0" t="inlineStr">
+        <x:is>
+          <x:t>URL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="4" t="inlineStr">
+        <x:is>
+          <x:t>https://support.microsoft.com/es-es/excel/functions/workday-intl-function</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="0" t="inlineStr">
+        <x:is>
+          <x:t>Consulta</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="4" t="inlineStr">
+        <x:is>
+          <x:t>12/10/2026 — Sintaxis y comportamiento contrastados para la ampliación de plazo; explicación de la plataforma autocontenida.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
